--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1208.62</v>
+        <v>1221.77</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>762.9299999999999</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1262.43</v>
+        <v>1257.13</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1010.01</v>
+        <v>1011.3</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21538.03</v>
+        <v>21523.32</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3162.34</v>
+        <v>3204.93</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1144.63</v>
+        <v>1172.47</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>822.5599999999999</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1325.76</v>
+        <v>1365.16</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3364.31</v>
+        <v>3464.31</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2021.97</v>
+        <v>2040.36</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1548.23</v>
+        <v>1562.02</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2546.96</v>
+        <v>2544.34</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1219.72</v>
+        <v>1238.83</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1037.12</v>
+        <v>1032.65</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1404.02</v>
+        <v>1397.97</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9187.98</v>
+        <v>8974.18</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>38506.95</v>
+        <v>37747.54</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4765.26</v>
+        <v>4785.06</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1049.82</v>
+        <v>1063.52</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>931.34</v>
+        <v>948.95</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1506.44</v>
+        <v>1535.08</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1405.7</v>
+        <v>1437.4</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3087.25</v>
+        <v>3107.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1423-29-CM25</t>
+          <t>1233607-41-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.701.012-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1221.77</v>
+        <v>1328.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3349-381-CM25</t>
+          <t>1423-29-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>60.701.012-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>768.21</v>
+        <v>1221.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1350296-2039-CM25</t>
+          <t>3349-381-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1257.13</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>628-507-CM25</t>
+          <t>1350296-2039-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1011.3</v>
+        <v>1257.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2404-20-CM26</t>
+          <t>628-507-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21523.32</v>
+        <v>1011.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1426397-12-CM26</t>
+          <t>2404-20-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3204.93</v>
+        <v>21523.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1346281-21-CM26</t>
+          <t>1426397-12-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1172.47</v>
+        <v>3204.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1346281-23-CM26</t>
+          <t>1346281-21-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>847</v>
+        <v>1172.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1346281-24-CM26</t>
+          <t>1346281-23-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1365.16</v>
+        <v>847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1346281-25-CM26</t>
+          <t>1346281-24-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3464.31</v>
+        <v>1365.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1476917-1-CM26</t>
+          <t>1346281-25-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SLEP IQUIQUE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2040.36</v>
+        <v>3464.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1426397-24-CM26</t>
+          <t>1476917-1-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SLEP IQUIQUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1562.02</v>
+        <v>2040.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3170-26-CM26</t>
+          <t>1426397-24-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2544.34</v>
+        <v>1562.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3352-27-CM26</t>
+          <t>3170-26-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1238.83</v>
+        <v>2544.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3145-85-CM26</t>
+          <t>3352-27-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1032.65</v>
+        <v>1238.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3145-87-CM26</t>
+          <t>3145-85-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1397.97</v>
+        <v>1032.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1426397-109-CM26</t>
+          <t>3145-87-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8974.18</v>
+        <v>1397.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3447-880-CM26</t>
+          <t>1426397-109-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>37747.54</v>
+        <v>8974.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1346281-58-CM26</t>
+          <t>3447-880-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4785.06</v>
+        <v>37747.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3447-995-CM26</t>
+          <t>1346281-58-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1063.52</v>
+        <v>4785.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3447-1031-CM26</t>
+          <t>3447-995-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>948.95</v>
+        <v>1063.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1346281-89-CM26</t>
+          <t>3447-1031-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1535.08</v>
+        <v>948.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1346281-90-CM26</t>
+          <t>1346281-89-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1437.4</v>
+        <v>1535.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5690-91-CM26</t>
+          <t>1346281-90-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,6 +1972,67 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
+        <v>1437.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5690-91-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>3107.37</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1233607-41-CM25</t>
+          <t>5513-4-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1328.09</v>
+        <v>37932.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1423-29-CM25</t>
+          <t>1426397-25-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.701.012-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1221.77</v>
+        <v>10008.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3349-381-CM25</t>
+          <t>618472-1-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>768.21</v>
+        <v>1207.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1350296-2039-CM25</t>
+          <t>3447-599-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1257.13</v>
+        <v>55162.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>628-507-CM25</t>
+          <t>908366-9-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CIBELES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.852-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1011.3</v>
+        <v>1097.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2404-20-CM26</t>
+          <t>1426397-49-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21523.32</v>
+        <v>21031.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1426397-12-CM26</t>
+          <t>1305552-29-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3204.93</v>
+        <v>6105.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1346281-21-CM26</t>
+          <t>1346281-55-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1172.47</v>
+        <v>2172.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1346281-23-CM26</t>
+          <t>3352-55-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>847</v>
+        <v>1111.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1346281-24-CM26</t>
+          <t>1426397-84-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1365.16</v>
+        <v>31305.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1346281-25-CM26</t>
+          <t>908366-24-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3464.31</v>
+        <v>730.1799999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1476917-1-CM26</t>
+          <t>1426397-139-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SLEP IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2040.36</v>
+        <v>2332.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1426397-24-CM26</t>
+          <t>1070620-12270-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1562.02</v>
+        <v>2325.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3170-26-CM26</t>
+          <t>5690-62-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2544.34</v>
+        <v>904.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3352-27-CM26</t>
+          <t>1070620-12618-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1238.83</v>
+        <v>1418.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3145-85-CM26</t>
+          <t>3145-408-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1032.65</v>
+        <v>824.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3145-87-CM26</t>
+          <t>1233607-41-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1397.97</v>
+        <v>1328.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1426397-109-CM26</t>
+          <t>1426397-182-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8974.18</v>
+        <v>7480.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3447-880-CM26</t>
+          <t>3352-188-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>37747.54</v>
+        <v>1211.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1346281-58-CM26</t>
+          <t>1070620-14391-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4785.06</v>
+        <v>1896.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3447-995-CM26</t>
+          <t>3352-210-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1063.52</v>
+        <v>846.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3447-1031-CM26</t>
+          <t>3352-209-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>948.95</v>
+        <v>1259.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1346281-89-CM26</t>
+          <t>3352-211-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1535.08</v>
+        <v>2188.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1346281-90-CM26</t>
+          <t>1171177-49-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1437.4</v>
+        <v>1572.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5690-91-CM26</t>
+          <t>935934-154-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.436.831-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2033,2142 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
+        <v>9749.889999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3352-236-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1985.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3352-237-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.967.556-6</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1157.77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2013-1202-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>3943.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1350296-1790-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>10787.97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1476917-3-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>11250.03</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5513-32-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.301.000-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>15771.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1417913-421-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>766.11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1346281-168-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>3019.92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1417913-419-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>765.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1423-29-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.701.012-9</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1221.77</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3349-381-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>768.21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1350296-2039-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1257.13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>628-507-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1011.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2404-20-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>21523.32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1426397-12-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>3204.93</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1346281-21-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1172.47</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1346281-23-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA WAY SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1346281-24-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1365.16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1346281-25-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>3464.31</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1476917-1-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SLEP IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>2040.36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1426397-24-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1562.02</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3170-26-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.941.300-8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>2544.34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3352-27-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA WAY SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.532.399-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1238.83</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3145-85-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Iª Brigada Aérea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1032.65</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3145-87-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.103.023-1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Iª Brigada Aérea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>1397.97</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1426397-109-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.980.910-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Iquique</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>8974.18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3447-880-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.967.556-6</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>37747.54</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1346281-58-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Comercial Agustin Limitada</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>4785.06</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3447-995-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>1063.52</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3447-1031-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>948.95</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1346281-89-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1535.08</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1346281-90-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1437.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>5690-91-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
         <v>3107.37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1346281-125-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>5209.26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1417913-667-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1230.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1426397-25-CM25</t>
+          <t>618472-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10008.22</v>
+        <v>1207.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>618472-1-CM25</t>
+          <t>1426397-25-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1207.66</v>
+        <v>10008.22</v>
       </c>
     </row>
     <row r="5">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3352-210-CM25</t>
+          <t>3352-209-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>846.74</v>
+        <v>1259.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3352-209-CM25</t>
+          <t>3352-211-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1259.52</v>
+        <v>2188.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3352-211-CM25</t>
+          <t>3352-210-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2188.53</v>
+        <v>846.74</v>
       </c>
     </row>
     <row r="25">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>628-507-CM25</t>
+          <t>2404-20-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1011.3</v>
+        <v>21523.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2404-20-CM26</t>
+          <t>1426397-12-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21523.32</v>
+        <v>3204.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1426397-12-CM26</t>
+          <t>1346281-21-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3204.93</v>
+        <v>1172.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1346281-21-CM26</t>
+          <t>1346281-23-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1172.47</v>
+        <v>847</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1346281-23-CM26</t>
+          <t>1346281-24-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>847</v>
+        <v>1365.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1346281-24-CM26</t>
+          <t>1346281-25-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1365.16</v>
+        <v>3464.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1346281-25-CM26</t>
+          <t>1476917-1-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3464.31</v>
+        <v>2040.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1476917-1-CM26</t>
+          <t>1426397-24-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SLEP IQUIQUE</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2040.36</v>
+        <v>1562.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1426397-24-CM26</t>
+          <t>3170-26-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1562.02</v>
+        <v>2544.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3170-26-CM26</t>
+          <t>3352-27-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2544.34</v>
+        <v>1238.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3352-27-CM26</t>
+          <t>3145-85-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1238.83</v>
+        <v>1032.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3145-85-CM26</t>
+          <t>3145-87-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1032.65</v>
+        <v>1397.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3145-87-CM26</t>
+          <t>1426397-109-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1397.97</v>
+        <v>8974.18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1426397-109-CM26</t>
+          <t>3447-880-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8974.18</v>
+        <v>37747.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3447-880-CM26</t>
+          <t>1346281-58-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>37747.54</v>
+        <v>4785.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1346281-58-CM26</t>
+          <t>3447-995-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4785.06</v>
+        <v>1063.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3447-995-CM26</t>
+          <t>3447-1031-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1063.52</v>
+        <v>948.95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3447-1031-CM26</t>
+          <t>1346281-89-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>948.95</v>
+        <v>1535.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1346281-89-CM26</t>
+          <t>1346281-90-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1535.08</v>
+        <v>1437.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1346281-90-CM26</t>
+          <t>5690-91-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1437.4</v>
+        <v>3107.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5690-91-CM26</t>
+          <t>1346281-125-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3107.37</v>
+        <v>5209.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1346281-125-CM26</t>
+          <t>1417913-667-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,22 +4067,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5209.26</v>
+        <v>1230.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1417913-667-CM26</t>
+          <t>5690-119-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1230.2</v>
+        <v>745.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>77.831.852-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1180,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1489,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1676,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1741,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2721,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3030,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3095,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3404,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3957,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -2294,7 +2294,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3713,7 +3717,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/tarapaca.xlsx
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
